--- a/MainBoard_Unlimited26/pin_MainBoard_Unlimited.xlsx
+++ b/MainBoard_Unlimited26/pin_MainBoard_Unlimited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo L13\OneDrive\Documents\GitHub\MainBoard-Transport-Unlimited2026\MainBoard_Unlimited26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BC4502-82BB-4BDE-A976-25C2723EDA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D6CBB1-6590-4C64-BBB3-18660DA14BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1480" yWindow="1480" windowWidth="14400" windowHeight="7270" xr2:uid="{44CCC2A1-F80A-465A-B763-4A7D61272D62}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
   <si>
     <t>komponen</t>
   </si>
@@ -102,45 +102,6 @@
     <t>ID-BAT</t>
   </si>
   <si>
-    <t>pin pca</t>
-  </si>
-  <si>
-    <t>PWM 2</t>
-  </si>
-  <si>
-    <t>PWM 1</t>
-  </si>
-  <si>
-    <t>PWM 3</t>
-  </si>
-  <si>
-    <t>PWM 4</t>
-  </si>
-  <si>
-    <t>PWM 5</t>
-  </si>
-  <si>
-    <t>PWM 6</t>
-  </si>
-  <si>
-    <t>PWM 7</t>
-  </si>
-  <si>
-    <t>PWM 8</t>
-  </si>
-  <si>
-    <t>PWM 9</t>
-  </si>
-  <si>
-    <t>PWM 10</t>
-  </si>
-  <si>
-    <t>PWM 11</t>
-  </si>
-  <si>
-    <t>PWM 12</t>
-  </si>
-  <si>
     <t>SDA</t>
   </si>
   <si>
@@ -157,13 +118,109 @@
   </si>
   <si>
     <t>vl53l0x</t>
+  </si>
+  <si>
+    <t>pin stm</t>
+  </si>
+  <si>
+    <t>ESP32 Devkit V1</t>
+  </si>
+  <si>
+    <t>STM32 Blue Pill</t>
+  </si>
+  <si>
+    <t>Koneksi</t>
+  </si>
+  <si>
+    <t>RX</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>PB8</t>
+  </si>
+  <si>
+    <t>PB9</t>
+  </si>
+  <si>
+    <t>PB6</t>
+  </si>
+  <si>
+    <t>PB7</t>
+  </si>
+  <si>
+    <t>PA10</t>
+  </si>
+  <si>
+    <t>PA11</t>
+  </si>
+  <si>
+    <t>PA8</t>
+  </si>
+  <si>
+    <t>PA9</t>
+  </si>
+  <si>
+    <t>PA7</t>
+  </si>
+  <si>
+    <t>PA6</t>
+  </si>
+  <si>
+    <t>PB1</t>
+  </si>
+  <si>
+    <t>PB0</t>
+  </si>
+  <si>
+    <t>TIM4_CH3</t>
+  </si>
+  <si>
+    <t>TIM4_CH4</t>
+  </si>
+  <si>
+    <t>TIM4_CH1</t>
+  </si>
+  <si>
+    <t>TIM4_CH2</t>
+  </si>
+  <si>
+    <t>TIM1_CH3</t>
+  </si>
+  <si>
+    <t>TIM1_CH4</t>
+  </si>
+  <si>
+    <t>TIM1_CH1</t>
+  </si>
+  <si>
+    <t>TIM1_CH2</t>
+  </si>
+  <si>
+    <t>TIM3_CH2</t>
+  </si>
+  <si>
+    <t>TIM3_CH1</t>
+  </si>
+  <si>
+    <t>TIM3_CH4</t>
+  </si>
+  <si>
+    <t>TIM3_CH3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,6 +241,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -193,7 +258,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -277,11 +342,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -291,6 +369,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -619,15 +707,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458D5EB6-CEBA-4A3D-93B9-057BBA8A07BF}">
-  <dimension ref="B2:M26"/>
+  <dimension ref="B2:N26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.90625" customWidth="1"/>
+    <col min="6" max="6" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,11 +727,12 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="E2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="8"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
@@ -650,20 +741,46 @@
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="1">
+        <v>16</v>
+      </c>
+      <c r="K4" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
@@ -672,20 +789,36 @@
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
@@ -694,20 +827,27 @@
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
@@ -716,20 +856,26 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -738,20 +884,26 @@
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
@@ -760,20 +912,26 @@
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
@@ -784,8 +942,9 @@
         <v>14</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
@@ -796,8 +955,9 @@
         <v>27</v>
       </c>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
         <v>14</v>
       </c>
@@ -808,8 +968,9 @@
         <v>26</v>
       </c>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
@@ -820,8 +981,9 @@
         <v>25</v>
       </c>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
         <v>16</v>
       </c>
@@ -832,143 +994,155 @@
         <v>33</v>
       </c>
       <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="1">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="1">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D22" s="1">
         <v>35</v>
       </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="1">
         <v>21</v>
       </c>
-      <c r="E21" s="2"/>
-      <c r="G21" s="5" t="s">
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="H23" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I21" s="1">
+      <c r="I23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="1">
         <v>21</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="L23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N23" s="3">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B22" s="6"/>
-      <c r="C22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D22" s="1">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B24" s="10"/>
+      <c r="C24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="1">
         <v>22</v>
       </c>
-      <c r="E22" s="2"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I22" s="1">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="1">
         <v>22</v>
       </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M22" s="4">
+      <c r="L24" s="12"/>
+      <c r="M24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B23" s="6"/>
-      <c r="C23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="1">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B25" s="10"/>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1">
         <v>19</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="1" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I23" s="1">
-        <v>11</v>
-      </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="4">
+      <c r="J25" s="1">
+        <v>19</v>
+      </c>
+      <c r="L25" s="12"/>
+      <c r="M25" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" s="4">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B24" s="7"/>
-      <c r="C24" s="1" t="s">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B26" s="11"/>
+      <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D26" s="1">
         <v>18</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="1" t="s">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I24" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B25" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="1">
-        <v>5</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B26" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="J26" s="1">
         <v>18</v>
       </c>
-      <c r="D26" s="1">
-        <v>13</v>
-      </c>
-      <c r="E26" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B21:B24"/>
-    <mergeCell ref="G21:G24"/>
-    <mergeCell ref="K21:K23"/>
+  <mergeCells count="7">
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="H23:H26"/>
+    <mergeCell ref="L23:L25"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
